--- a/customerapp/testdata/AugMontData.xlsx
+++ b/customerapp/testdata/AugMontData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kamlesh Diwan\augmontCustomerApp\customerApp\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kamlesh Diwan\augmontCustomerApp\customerapp\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B08D36C-4E7B-4D6E-AE8B-FB2401C7112B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAA914B-6E65-481E-8E8E-569EF2C9D8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Username</t>
   </si>
@@ -65,6 +65,18 @@
   </si>
   <si>
     <t>Manually Entered Amount</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>Weekly Sip</t>
+  </si>
+  <si>
+    <t>Monthly Sip</t>
   </si>
 </sst>
 </file>
@@ -114,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -130,6 +142,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -442,23 +457,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C4A08B-FB89-451B-B0A8-BE06111BE5D2}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="4"/>
+    <col min="2" max="2" width="17.5703125" style="4" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
     <col min="5" max="5" width="17.140625" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="4">
         <v>1</v>
       </c>
       <c r="C1">
@@ -480,11 +497,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -505,8 +522,9 @@
       <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -532,7 +550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -556,6 +574,40 @@
       </c>
       <c r="H4" s="4" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4">
+        <v>100001</v>
+      </c>
+      <c r="D5" s="4">
+        <v>100001</v>
+      </c>
+      <c r="H5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4">
+        <v>100001</v>
+      </c>
+      <c r="D6" s="4">
+        <v>100001</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
